--- a/paper/tables/merged_coef.xlsx
+++ b/paper/tables/merged_coef.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marie\rep_codes\udder_project\paper\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{562DC9B5-7A70-4BB3-8D9B-3E547D69D2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80DBD089-42EE-478D-88F8-277F0627A820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1CD3770C-D87B-40B1-9521-5FD13720A64B}"/>
   </bookViews>
   <sheets>
     <sheet name="merged_coef" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="17">
   <si>
     <t>Row.names</t>
   </si>
@@ -65,6 +78,12 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>mean_flow.x</t>
+  </si>
+  <si>
+    <t>mean_flow.y</t>
   </si>
 </sst>
 </file>
@@ -925,10 +944,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B97F07E-7367-4E68-B552-0FD6D8E601A5}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -945,19 +964,34 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" t="s">
+      <c r="P1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -973,24 +1007,39 @@
       <c r="E2">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="G2" t="str">
-        <f>_xlfn.CONCAT(B2,IF(B14&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>-0.69\textsuperscript{*}</v>
-      </c>
-      <c r="H2" t="str">
-        <f>_xlfn.CONCAT(C2,IF(C14&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>-0.353\textsuperscript{*}</v>
-      </c>
-      <c r="I2" t="str">
-        <f>_xlfn.CONCAT(D2,IF(D14&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.07</v>
-      </c>
-      <c r="J2" t="str">
-        <f>_xlfn.CONCAT(E2,IF(E14&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.043</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="I2">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="J2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M2" t="str">
+        <f>_xlfn.CONCAT(B2,"$\pm$", H2,IF(B14&lt;=0.05,"\textsuperscript{*}",""))</f>
+        <v>-0.69$\pm$0.086\textsuperscript{*}</v>
+      </c>
+      <c r="N2" t="str">
+        <f>_xlfn.CONCAT(C2,"$\pm$", I2,IF(C14&lt;=0.05,"\textsuperscript{*}",""))</f>
+        <v>-0.353$\pm$0.132\textsuperscript{*}</v>
+      </c>
+      <c r="O2" t="str">
+        <f>_xlfn.CONCAT(D2,"$\pm$", J2,IF(D14&lt;=0.05,"\textsuperscript{*}",""))</f>
+        <v>0.07$\pm$0.14</v>
+      </c>
+      <c r="P2" t="str">
+        <f>_xlfn.CONCAT(E2,"$\pm$", K2,IF(E14&lt;=0.05,"\textsuperscript{*}",""))</f>
+        <v>0.043$\pm$0.14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1006,24 +1055,39 @@
       <c r="E3">
         <v>4.7E-2</v>
       </c>
-      <c r="G3" t="str">
-        <f>_xlfn.CONCAT(B3,IF(B15&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.187\textsuperscript{*}</v>
-      </c>
-      <c r="H3" t="str">
-        <f>_xlfn.CONCAT(C3,IF(C15&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>-0.036</v>
-      </c>
-      <c r="I3" t="str">
-        <f>_xlfn.CONCAT(D3,IF(D15&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.022</v>
-      </c>
-      <c r="J3" t="str">
-        <f>_xlfn.CONCAT(E3,IF(E15&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.047</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I3">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="J3">
+        <v>5.5E-2</v>
+      </c>
+      <c r="K3">
+        <v>5.5E-2</v>
+      </c>
+      <c r="M3" t="str">
+        <f t="shared" ref="M3:P11" si="0">_xlfn.CONCAT(B3,"$\pm$", H3,IF(B15&lt;=0.05,"\textsuperscript{*}",""))</f>
+        <v>0.187$\pm$0.054\textsuperscript{*}</v>
+      </c>
+      <c r="N3" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.036$\pm$0.067</v>
+      </c>
+      <c r="O3" t="str">
+        <f t="shared" si="0"/>
+        <v>0.022$\pm$0.055</v>
+      </c>
+      <c r="P3" t="str">
+        <f t="shared" si="0"/>
+        <v>0.047$\pm$0.055</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1039,24 +1103,39 @@
       <c r="E4">
         <v>-9.5000000000000001E-2</v>
       </c>
-      <c r="G4" t="str">
-        <f>_xlfn.CONCAT(B4,IF(B16&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.036</v>
-      </c>
-      <c r="H4" t="str">
-        <f>_xlfn.CONCAT(C4,IF(C16&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>-0.025</v>
-      </c>
-      <c r="I4" t="str">
-        <f>_xlfn.CONCAT(D4,IF(D16&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>-0.079</v>
-      </c>
-      <c r="J4" t="str">
-        <f>_xlfn.CONCAT(E4,IF(E16&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>-0.095</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="I4">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="J4">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="K4">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="M4" t="str">
+        <f t="shared" si="0"/>
+        <v>0.036$\pm$0.048</v>
+      </c>
+      <c r="N4" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.025$\pm$0.072</v>
+      </c>
+      <c r="O4" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.079$\pm$0.079</v>
+      </c>
+      <c r="P4" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.095$\pm$0.079</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1072,24 +1151,39 @@
       <c r="E5">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="G5" t="str">
-        <f>_xlfn.CONCAT(B5,IF(B17&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>-0.066</v>
-      </c>
-      <c r="H5" t="str">
-        <f>_xlfn.CONCAT(C5,IF(C17&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.036</v>
-      </c>
-      <c r="I5" t="str">
-        <f>_xlfn.CONCAT(D5,IF(D17&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.087</v>
-      </c>
-      <c r="J5" t="str">
-        <f>_xlfn.CONCAT(E5,IF(E17&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.059</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="I5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J5">
+        <v>0.08</v>
+      </c>
+      <c r="K5">
+        <v>0.08</v>
+      </c>
+      <c r="M5" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.066$\pm$0.046</v>
+      </c>
+      <c r="N5" t="str">
+        <f t="shared" si="0"/>
+        <v>0.036$\pm$0.07</v>
+      </c>
+      <c r="O5" t="str">
+        <f t="shared" si="0"/>
+        <v>0.087$\pm$0.08</v>
+      </c>
+      <c r="P5" t="str">
+        <f t="shared" si="0"/>
+        <v>0.059$\pm$0.08</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1105,24 +1199,39 @@
       <c r="E6">
         <v>2.7E-2</v>
       </c>
-      <c r="G6" t="str">
-        <f>_xlfn.CONCAT(B6,IF(B18&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.002</v>
-      </c>
-      <c r="H6" t="str">
-        <f>_xlfn.CONCAT(C6,IF(C18&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>-0.087\textsuperscript{*}</v>
-      </c>
-      <c r="I6" t="str">
-        <f>_xlfn.CONCAT(D6,IF(D18&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.026</v>
-      </c>
-      <c r="J6" t="str">
-        <f>_xlfn.CONCAT(E6,IF(E18&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.027</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>0.03</v>
+      </c>
+      <c r="I6">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="J6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M6" t="str">
+        <f t="shared" si="0"/>
+        <v>0.002$\pm$0.03</v>
+      </c>
+      <c r="N6" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.087$\pm$0.036\textsuperscript{*}</v>
+      </c>
+      <c r="O6" t="str">
+        <f t="shared" si="0"/>
+        <v>0.026$\pm$0.029</v>
+      </c>
+      <c r="P6" t="str">
+        <f t="shared" si="0"/>
+        <v>0.027$\pm$0.029</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1138,24 +1247,39 @@
       <c r="E7">
         <v>-0.27800000000000002</v>
       </c>
-      <c r="G7" t="str">
-        <f>_xlfn.CONCAT(B7,IF(B19&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.477\textsuperscript{*}</v>
-      </c>
-      <c r="H7" t="str">
-        <f>_xlfn.CONCAT(C7,IF(C19&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>-0.032</v>
-      </c>
-      <c r="I7" t="str">
-        <f>_xlfn.CONCAT(D7,IF(D19&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>-0.318\textsuperscript{*}</v>
-      </c>
-      <c r="J7" t="str">
-        <f>_xlfn.CONCAT(E7,IF(E19&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>-0.278\textsuperscript{*}</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>4.7E-2</v>
+      </c>
+      <c r="I7">
+        <v>7.8E-2</v>
+      </c>
+      <c r="J7">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="K7">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="M7" t="str">
+        <f t="shared" si="0"/>
+        <v>0.477$\pm$0.047\textsuperscript{*}</v>
+      </c>
+      <c r="N7" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.032$\pm$0.078</v>
+      </c>
+      <c r="O7" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.318$\pm$0.085\textsuperscript{*}</v>
+      </c>
+      <c r="P7" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.278$\pm$0.085\textsuperscript{*}</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1171,24 +1295,39 @@
       <c r="E8">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G8" t="str">
-        <f>_xlfn.CONCAT(B8,IF(B20&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.073</v>
-      </c>
-      <c r="H8" t="str">
-        <f>_xlfn.CONCAT(C8,IF(C20&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.031</v>
-      </c>
-      <c r="I8" t="str">
-        <f>_xlfn.CONCAT(D8,IF(D20&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.038</v>
-      </c>
-      <c r="J8" t="str">
-        <f>_xlfn.CONCAT(E8,IF(E20&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.07</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8">
+        <v>3.9E-2</v>
+      </c>
+      <c r="I8">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J8">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="K8">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" si="0"/>
+        <v>0.073$\pm$0.039</v>
+      </c>
+      <c r="N8" t="str">
+        <f t="shared" si="0"/>
+        <v>0.031$\pm$0.049</v>
+      </c>
+      <c r="O8" t="str">
+        <f t="shared" si="0"/>
+        <v>0.038$\pm$0.041</v>
+      </c>
+      <c r="P8" t="str">
+        <f t="shared" si="0"/>
+        <v>0.07$\pm$0.041</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1204,24 +1343,39 @@
       <c r="E9">
         <v>-7.0999999999999994E-2</v>
       </c>
-      <c r="G9" t="str">
-        <f>_xlfn.CONCAT(B9,IF(B21&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.549\textsuperscript{*}</v>
-      </c>
-      <c r="H9" t="str">
-        <f>_xlfn.CONCAT(C9,IF(C21&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>-0.095</v>
-      </c>
-      <c r="I9" t="str">
-        <f>_xlfn.CONCAT(D9,IF(D21&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>-0.079</v>
-      </c>
-      <c r="J9" t="str">
-        <f>_xlfn.CONCAT(E9,IF(E21&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>-0.071</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9">
+        <v>0.107</v>
+      </c>
+      <c r="I9">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="J9">
+        <v>0.11</v>
+      </c>
+      <c r="K9">
+        <v>0.11</v>
+      </c>
+      <c r="M9" t="str">
+        <f t="shared" si="0"/>
+        <v>0.549$\pm$0.107\textsuperscript{*}</v>
+      </c>
+      <c r="N9" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.095$\pm$0.135</v>
+      </c>
+      <c r="O9" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.079$\pm$0.11</v>
+      </c>
+      <c r="P9" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.071$\pm$0.11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1237,24 +1391,39 @@
       <c r="E10">
         <v>2.3E-2</v>
       </c>
-      <c r="G10" t="str">
-        <f>_xlfn.CONCAT(B10,IF(B22&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.609\textsuperscript{*}</v>
-      </c>
-      <c r="H10" t="str">
-        <f>_xlfn.CONCAT(C10,IF(C22&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.667\textsuperscript{*}</v>
-      </c>
-      <c r="I10" t="str">
-        <f>_xlfn.CONCAT(D10,IF(D22&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>-0.016</v>
-      </c>
-      <c r="J10" t="str">
-        <f>_xlfn.CONCAT(E10,IF(E22&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.023</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>0.1</v>
+      </c>
+      <c r="I10">
+        <v>0.156</v>
+      </c>
+      <c r="J10">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="K10">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="M10" t="str">
+        <f t="shared" si="0"/>
+        <v>0.609$\pm$0.1\textsuperscript{*}</v>
+      </c>
+      <c r="N10" t="str">
+        <f t="shared" si="0"/>
+        <v>0.667$\pm$0.156\textsuperscript{*}</v>
+      </c>
+      <c r="O10" t="str">
+        <f t="shared" si="0"/>
+        <v>-0.016$\pm$0.173</v>
+      </c>
+      <c r="P10" t="str">
+        <f t="shared" si="0"/>
+        <v>0.023$\pm$0.173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -1270,24 +1439,39 @@
       <c r="E11">
         <v>0.46700000000000003</v>
       </c>
-      <c r="G11" t="str">
-        <f>_xlfn.CONCAT(B11,IF(B23&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>NA</v>
-      </c>
-      <c r="H11" t="str">
-        <f>_xlfn.CONCAT(C11,IF(C23&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.107</v>
-      </c>
-      <c r="I11" t="str">
-        <f>_xlfn.CONCAT(D11,IF(D23&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.54\textsuperscript{*}</v>
-      </c>
-      <c r="J11" t="str">
-        <f>_xlfn.CONCAT(E11,IF(E23&lt;=0.05,"\textsuperscript{*}",""))</f>
-        <v>0.467\textsuperscript{*}</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J11">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="K11">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="M11" t="str">
+        <f t="shared" si="0"/>
+        <v>NA$\pm$NA</v>
+      </c>
+      <c r="N11" t="str">
+        <f t="shared" si="0"/>
+        <v>0.107$\pm$0.066</v>
+      </c>
+      <c r="O11" t="str">
+        <f t="shared" si="0"/>
+        <v>0.54$\pm$0.056\textsuperscript{*}</v>
+      </c>
+      <c r="P11" t="str">
+        <f t="shared" si="0"/>
+        <v>0.467$\pm$0.056\textsuperscript{*}</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -1316,7 +1500,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -1333,11 +1517,11 @@
         <v>0.76</v>
       </c>
       <c r="G14" t="str">
-        <f>_xlfn.CONCAT(A2, " &amp;", G2,  " &amp; ",H2, " &amp; ",I2, " &amp; ",J2,  " \\")</f>
-        <v>(Intercept) &amp;-0.69\textsuperscript{*} &amp; -0.353\textsuperscript{*} &amp; 0.07 &amp; 0.043 \\</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(A2, " &amp;", M2,  " &amp; ",N2, " &amp; ",O2, " &amp; ",P2,  " \\")</f>
+        <v>(Intercept) &amp;-0.69$\pm$0.086\textsuperscript{*} &amp; -0.353$\pm$0.132\textsuperscript{*} &amp; 0.07$\pm$0.14 &amp; 0.043$\pm$0.14 \\</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1354,11 +1538,11 @@
         <v>0.44400000000000001</v>
       </c>
       <c r="G15" t="str">
-        <f t="shared" ref="G15:G23" si="0">_xlfn.CONCAT(A3, " &amp;", G3,  " &amp; ",H3, " &amp; ",I3, " &amp; ",J3,  " \\")</f>
-        <v>area &amp;0.187\textsuperscript{*} &amp; -0.036 &amp; 0.022 &amp; 0.047 \\</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(A3, " &amp;", M3,  " &amp; ",N3, " &amp; ",O3, " &amp; ",P3,  " \\")</f>
+        <v>area &amp;0.187$\pm$0.054\textsuperscript{*} &amp; -0.036$\pm$0.067 &amp; 0.022$\pm$0.055 &amp; 0.047$\pm$0.055 \\</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1375,8 +1559,8 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="G16" t="str">
-        <f t="shared" si="0"/>
-        <v>circ &amp;0.036 &amp; -0.025 &amp; -0.079 &amp; -0.095 \\</v>
+        <f>_xlfn.CONCAT(A4, " &amp;", M4,  " &amp; ",N4, " &amp; ",O4, " &amp; ",P4,  " \\")</f>
+        <v>circ &amp;0.036$\pm$0.048 &amp; -0.025$\pm$0.072 &amp; -0.079$\pm$0.079 &amp; -0.095$\pm$0.079 \\</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1396,8 +1580,8 @@
         <v>0.45400000000000001</v>
       </c>
       <c r="G17" t="str">
-        <f t="shared" si="0"/>
-        <v>days_in_milk &amp;-0.066 &amp; 0.036 &amp; 0.087 &amp; 0.059 \\</v>
+        <f>_xlfn.CONCAT(A5, " &amp;", M5,  " &amp; ",N5, " &amp; ",O5, " &amp; ",P5,  " \\")</f>
+        <v>days_in_milk &amp;-0.066$\pm$0.046 &amp; 0.036$\pm$0.07 &amp; 0.087$\pm$0.08 &amp; 0.059$\pm$0.08 \\</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1417,8 +1601,8 @@
         <v>0.40799999999999997</v>
       </c>
       <c r="G18" t="str">
-        <f t="shared" si="0"/>
-        <v>exc &amp;0.002 &amp; -0.087\textsuperscript{*} &amp; 0.026 &amp; 0.027 \\</v>
+        <f>_xlfn.CONCAT(A6, " &amp;", M6,  " &amp; ",N6, " &amp; ",O6, " &amp; ",P6,  " \\")</f>
+        <v>exc &amp;0.002$\pm$0.03 &amp; -0.087$\pm$0.036\textsuperscript{*} &amp; 0.026$\pm$0.029 &amp; 0.027$\pm$0.029 \\</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1438,8 +1622,8 @@
         <v>1E-3</v>
       </c>
       <c r="G19" t="str">
-        <f t="shared" si="0"/>
-        <v>interval_sec &amp;0.477\textsuperscript{*} &amp; -0.032 &amp; -0.318\textsuperscript{*} &amp; -0.278\textsuperscript{*} \\</v>
+        <f>_xlfn.CONCAT(A7, " &amp;", M7,  " &amp; ",N7, " &amp; ",O7, " &amp; ",P7,  " \\")</f>
+        <v>interval_sec &amp;0.477$\pm$0.047\textsuperscript{*} &amp; -0.032$\pm$0.078 &amp; -0.318$\pm$0.085\textsuperscript{*} &amp; -0.278$\pm$0.085\textsuperscript{*} \\</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1459,8 +1643,8 @@
         <v>0.125</v>
       </c>
       <c r="G20" t="str">
-        <f t="shared" si="0"/>
-        <v>len &amp;0.073 &amp; 0.031 &amp; 0.038 &amp; 0.07 \\</v>
+        <f>_xlfn.CONCAT(A8, " &amp;", M8,  " &amp; ",N8, " &amp; ",O8, " &amp; ",P8,  " \\")</f>
+        <v>len &amp;0.073$\pm$0.039 &amp; 0.031$\pm$0.049 &amp; 0.038$\pm$0.041 &amp; 0.07$\pm$0.041 \\</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1480,8 +1664,8 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="G21" t="str">
-        <f t="shared" si="0"/>
-        <v>locationrear &amp;0.549\textsuperscript{*} &amp; -0.095 &amp; -0.079 &amp; -0.071 \\</v>
+        <f>_xlfn.CONCAT(A9, " &amp;", M9,  " &amp; ",N9, " &amp; ",O9, " &amp; ",P9,  " \\")</f>
+        <v>locationrear &amp;0.549$\pm$0.107\textsuperscript{*} &amp; -0.095$\pm$0.135 &amp; -0.079$\pm$0.11 &amp; -0.071$\pm$0.11 \\</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1501,8 +1685,8 @@
         <v>0.89300000000000002</v>
       </c>
       <c r="G22" t="str">
-        <f t="shared" si="0"/>
-        <v>parity1 &amp;0.609\textsuperscript{*} &amp; 0.667\textsuperscript{*} &amp; -0.016 &amp; 0.023 \\</v>
+        <f>_xlfn.CONCAT(A10, " &amp;", M10,  " &amp; ",N10, " &amp; ",O10, " &amp; ",P10,  " \\")</f>
+        <v>parity1 &amp;0.609$\pm$0.1\textsuperscript{*} &amp; 0.667$\pm$0.156\textsuperscript{*} &amp; -0.016$\pm$0.173 &amp; 0.023$\pm$0.173 \\</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1522,8 +1706,8 @@
         <v>0</v>
       </c>
       <c r="G23" t="str">
-        <f t="shared" si="0"/>
-        <v>yield &amp;NA &amp; 0.107 &amp; 0.54\textsuperscript{*} &amp; 0.467\textsuperscript{*} \\</v>
+        <f>_xlfn.CONCAT(A11, " &amp;", M11,  " &amp; ",N11, " &amp; ",O11, " &amp; ",P11,  " \\")</f>
+        <v>yield &amp;NA$\pm$NA &amp; 0.107$\pm$0.066 &amp; 0.54$\pm$0.056\textsuperscript{*} &amp; 0.467$\pm$0.056\textsuperscript{*} \\</v>
       </c>
     </row>
   </sheetData>
